--- a/Department_BillableData_Application Performance Monitoring.xlsx
+++ b/Department_BillableData_Application Performance Monitoring.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Billable Type</t>
   </si>
@@ -21,12 +21,6 @@
   </si>
   <si>
     <t>Application Performance Monitoring</t>
-  </si>
-  <si>
-    <t>Bench</t>
-  </si>
-  <si>
-    <t>Fixed Cost</t>
   </si>
   <si>
     <t>InternalRNDProducts</t>
@@ -117,11 +111,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.74609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.0859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -142,7 +136,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="4">
@@ -150,23 +144,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>
